--- a/data/trans_orig/P58-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P58-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2007</t>
+          <t>Población según su lugar de nacimiento en 2007 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17650</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40351</t>
+          <t>41024</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15332</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39750</t>
+          <t>39293</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36556</t>
+          <t>37055</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70717</t>
+          <t>70262</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15433</t>
+          <t>16049</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40555</t>
+          <t>39545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10047</t>
+          <t>9963</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>28492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30473</t>
+          <t>30357</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59976</t>
+          <t>58642</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>203656</t>
+          <t>204666</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>233821</t>
+          <t>235011</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>202215</t>
+          <t>203996</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>231114</t>
+          <t>231693</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>417205</t>
+          <t>417852</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>458106</t>
+          <t>457846</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,76%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31423</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>14287</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38250</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27182</t>
+          <t>28026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60237</t>
+          <t>59016</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26053</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57731</t>
+          <t>58261</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15049</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>35553</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46668</t>
+          <t>46581</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>86772</t>
+          <t>83463</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>415801</t>
+          <t>411615</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>452327</t>
+          <t>451614</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>438997</t>
+          <t>439027</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>469816</t>
+          <t>469458</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>864988</t>
+          <t>867119</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>914780</t>
+          <t>912455</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15069</t>
+          <t>13680</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15878</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23051</t>
+          <t>22924</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>18870</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44137</t>
+          <t>45904</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11992</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30535</t>
+          <t>30904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34562</t>
+          <t>34012</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66440</t>
+          <t>66638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>268969</t>
+          <t>267967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296299</t>
+          <t>296406</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>297141</t>
+          <t>296754</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>318524</t>
+          <t>319178</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>573370</t>
+          <t>575028</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>609778</t>
+          <t>609282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>9689</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31285</t>
+          <t>32529</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30560</t>
+          <t>29317</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24370</t>
+          <t>24562</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52396</t>
+          <t>54598</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13493</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36498</t>
+          <t>36653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,82 +2229,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>10,22%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>34229</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>23975</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>47577</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>57732</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>42598</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>74297</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>10,18%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>34229</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>23192</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>46388</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>12,49%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>57732</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>41543</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>75574</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>299137</t>
+          <t>298833</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>330382</t>
+          <t>330208</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>302582</t>
+          <t>303204</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>332034</t>
+          <t>332008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>613262</t>
+          <t>614215</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>656114</t>
+          <t>657422</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12011</t>
+          <t>11556</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31734</t>
+          <t>32474</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12782</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34733</t>
+          <t>33657</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27911</t>
+          <t>29018</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58479</t>
+          <t>58481</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30870</t>
+          <t>32408</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23279</t>
+          <t>23325</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21591</t>
+          <t>22414</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46600</t>
+          <t>49751</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>148832</t>
+          <t>148746</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>176153</t>
+          <t>176311</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>157789</t>
+          <t>158497</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>183562</t>
+          <t>183872</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>315593</t>
+          <t>315175</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>353598</t>
+          <t>352173</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,69%</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>12705</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1654</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13286</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18420</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26444</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>14925</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34187</t>
+          <t>35270</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25157</t>
+          <t>24675</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52412</t>
+          <t>53879</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>240768</t>
+          <t>239897</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>261789</t>
+          <t>261749</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>237129</t>
+          <t>235294</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>260602</t>
+          <t>258908</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>487105</t>
+          <t>485579</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>515772</t>
+          <t>517563</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>62682</t>
+          <t>60170</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>104039</t>
+          <t>102037</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>74322</t>
+          <t>73897</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>114863</t>
+          <t>118022</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>143834</t>
+          <t>142813</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>201223</t>
+          <t>202644</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>36180</t>
+          <t>36114</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>69743</t>
+          <t>70365</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>55559</t>
+          <t>55278</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>89084</t>
+          <t>89440</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>102332</t>
+          <t>101645</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>147720</t>
+          <t>150087</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>457254</t>
+          <t>456552</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>504348</t>
+          <t>506120</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>447089</t>
+          <t>449537</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>495806</t>
+          <t>498751</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>923986</t>
+          <t>917387</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>989606</t>
+          <t>989038</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,92%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>20265</t>
+          <t>19442</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>46004</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19511</t>
+          <t>20250</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>49026</t>
+          <t>49135</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>46545</t>
+          <t>46697</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>84495</t>
+          <t>87204</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>49768</t>
+          <t>48192</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>88681</t>
+          <t>89419</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>33872</t>
+          <t>33960</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>64212</t>
+          <t>62592</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>93117</t>
+          <t>91275</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>140452</t>
+          <t>140578</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>620049</t>
+          <t>619762</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>665177</t>
+          <t>667198</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>681494</t>
+          <t>683329</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>722187</t>
+          <t>723491</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1318464</t>
+          <t>1318145</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1376711</t>
+          <t>1377517</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>175089</t>
+          <t>174306</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>239375</t>
+          <t>239426</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>188925</t>
+          <t>192710</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>260829</t>
+          <t>260917</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>385425</t>
+          <t>381417</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>482913</t>
+          <t>484671</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>233863</t>
+          <t>235995</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>314410</t>
+          <t>316319</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>219556</t>
+          <t>220515</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>280947</t>
+          <t>282692</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>470374</t>
+          <t>476262</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>575599</t>
+          <t>580058</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2746504</t>
+          <t>2749724</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2845669</t>
+          <t>2847351</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2853356</t>
+          <t>2858073</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2950493</t>
+          <t>2946200</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5635560</t>
+          <t>5630879</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5771939</t>
+          <t>5772031</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2012</t>
+          <t>Población según su lugar de nacimiento en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43488</t>
+          <t>44178</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71955</t>
+          <t>74579</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32138</t>
+          <t>31024</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56889</t>
+          <t>57830</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80613</t>
+          <t>82187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118620</t>
+          <t>122697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25036</t>
+          <t>25791</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56648</t>
+          <t>56440</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31860</t>
+          <t>30563</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62765</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65162</t>
+          <t>64245</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110230</t>
+          <t>108077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>180435</t>
+          <t>178638</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>217585</t>
+          <t>215449</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>179888</t>
+          <t>179698</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>216140</t>
+          <t>215575</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>370668</t>
+          <t>367568</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>421524</t>
+          <t>422374</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,57%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>10339</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29219</t>
+          <t>29283</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>12427</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32256</t>
+          <t>31360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27743</t>
+          <t>27605</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55143</t>
+          <t>54903</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47334</t>
+          <t>46954</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88503</t>
+          <t>87167</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36678</t>
+          <t>36468</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72929</t>
+          <t>73120</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>93376</t>
+          <t>91977</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>146121</t>
+          <t>146566</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>398087</t>
+          <t>399450</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>440590</t>
+          <t>441667</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>429439</t>
+          <t>431471</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>468189</t>
+          <t>470445</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>840820</t>
+          <t>839796</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>898264</t>
+          <t>898757</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,32%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>11088</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17457</t>
+          <t>17938</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23873</t>
+          <t>24573</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12096</t>
+          <t>12380</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37551</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20230</t>
+          <t>20276</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49067</t>
+          <t>52104</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38440</t>
+          <t>37914</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75195</t>
+          <t>74735</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>281934</t>
+          <t>281640</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>308916</t>
+          <t>308643</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>281636</t>
+          <t>280281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>313186</t>
+          <t>312188</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>574747</t>
+          <t>574537</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>614135</t>
+          <t>615084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30940</t>
+          <t>31191</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10453</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29068</t>
+          <t>29629</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>25872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53165</t>
+          <t>53008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24188</t>
+          <t>24180</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57627</t>
+          <t>57883</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26607</t>
+          <t>26299</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58049</t>
+          <t>56927</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57542</t>
+          <t>57731</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101629</t>
+          <t>103958</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>296174</t>
+          <t>295949</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>331773</t>
+          <t>331293</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>312363</t>
+          <t>313288</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>346839</t>
+          <t>346689</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>621767</t>
+          <t>619929</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>672858</t>
+          <t>671223</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15168</t>
+          <t>15347</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13878</t>
+          <t>14077</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>7313</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23121</t>
+          <t>23663</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8037</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29973</t>
+          <t>29125</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>9256</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31763</t>
+          <t>31744</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21134</t>
+          <t>21426</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>51664</t>
+          <t>50606</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173224</t>
+          <t>175623</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>199010</t>
+          <t>200466</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>180469</t>
+          <t>179316</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204746</t>
+          <t>203918</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>367788</t>
+          <t>365330</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>398412</t>
+          <t>399005</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>11578</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>18051</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,42 +7403,42 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>14391</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>8235</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>25048</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>1,49%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>14391</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>8372</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>25026</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>14861</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44937</t>
+          <t>43122</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10815</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33373</t>
+          <t>33291</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32819</t>
+          <t>31613</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67771</t>
+          <t>66400</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>225881</t>
+          <t>225436</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>254289</t>
+          <t>254824</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>236240</t>
+          <t>235956</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>261833</t>
+          <t>261700</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>470472</t>
+          <t>472556</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>509307</t>
+          <t>507771</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>58312</t>
+          <t>58378</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>96986</t>
+          <t>94879</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>82943</t>
+          <t>83263</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>124195</t>
+          <t>123078</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>152732</t>
+          <t>151257</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>207375</t>
+          <t>203939</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>63297</t>
+          <t>64211</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>109096</t>
+          <t>110574</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>63304</t>
+          <t>62050</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>109200</t>
+          <t>106986</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>139353</t>
+          <t>137094</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>201439</t>
+          <t>200323</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>475010</t>
+          <t>476054</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>527560</t>
+          <t>529091</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>482503</t>
+          <t>480682</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>534197</t>
+          <t>533587</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>972502</t>
+          <t>972444</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1046754</t>
+          <t>1046450</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>13780</t>
+          <t>13490</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>36601</t>
+          <t>36622</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>12390</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>33832</t>
+          <t>32835</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>31997</t>
+          <t>30996</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>59655</t>
+          <t>61454</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>43581</t>
+          <t>46367</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>90268</t>
+          <t>90514</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>43888</t>
+          <t>44571</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>82593</t>
+          <t>83238</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>98726</t>
+          <t>100191</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>160748</t>
+          <t>157936</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>663726</t>
+          <t>664742</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>713881</t>
+          <t>712559</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>717458</t>
+          <t>718210</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>760600</t>
+          <t>759716</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1395465</t>
+          <t>1397893</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1460344</t>
+          <t>1460034</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>179591</t>
+          <t>180123</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>239642</t>
+          <t>242768</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>199087</t>
+          <t>202050</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>264604</t>
+          <t>261790</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>393752</t>
+          <t>400250</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>485907</t>
+          <t>484349</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>312621</t>
+          <t>314381</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>412346</t>
+          <t>416613</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>306152</t>
+          <t>308447</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>408217</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>641348</t>
+          <t>645546</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>777150</t>
+          <t>786431</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2806691</t>
+          <t>2795138</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2912479</t>
+          <t>2910291</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2920951</t>
+          <t>2918346</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3030426</t>
+          <t>3027045</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5759187</t>
+          <t>5751375</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5913484</t>
+          <t>5904723</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2016</t>
+          <t>Población según su lugar de nacimiento en 2016 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54739</t>
+          <t>54829</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87512</t>
+          <t>87397</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43619</t>
+          <t>42918</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70096</t>
+          <t>69377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104516</t>
+          <t>105579</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147862</t>
+          <t>145860</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21172</t>
+          <t>22207</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48548</t>
+          <t>52271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26448</t>
+          <t>25464</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54943</t>
+          <t>54910</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54382</t>
+          <t>54994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95357</t>
+          <t>94939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>172235</t>
+          <t>170936</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>207112</t>
+          <t>208519</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>175506</t>
+          <t>178083</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>209918</t>
+          <t>211670</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>360123</t>
+          <t>360383</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>408964</t>
+          <t>410982</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,56%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22052</t>
+          <t>22776</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>21952</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15420</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>37416</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19454</t>
+          <t>19276</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47358</t>
+          <t>47524</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>14281</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39251</t>
+          <t>41755</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39778</t>
+          <t>40387</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>77430</t>
+          <t>77067</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>442337</t>
+          <t>441158</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>473866</t>
+          <t>473470</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>469049</t>
+          <t>468994</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>498428</t>
+          <t>497744</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>918909</t>
+          <t>920903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>964101</t>
+          <t>964006</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12111</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25912</t>
+          <t>25841</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13894</t>
+          <t>13742</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32842</t>
+          <t>32299</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15932</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38932</t>
+          <t>39970</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>23054</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51986</t>
+          <t>52156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44973</t>
+          <t>45715</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80882</t>
+          <t>82164</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>274237</t>
+          <t>271330</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>298261</t>
+          <t>298354</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>266739</t>
+          <t>266397</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>297676</t>
+          <t>297743</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>550204</t>
+          <t>549837</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>589256</t>
+          <t>590579</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24360</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50275</t>
+          <t>49242</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21708</t>
+          <t>22185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>44238</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53743</t>
+          <t>52890</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85904</t>
+          <t>87686</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30249</t>
+          <t>30265</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60943</t>
+          <t>62519</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41764</t>
+          <t>41338</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77964</t>
+          <t>79571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>82385</t>
+          <t>81762</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>129646</t>
+          <t>127162</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>269183</t>
+          <t>269964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>305835</t>
+          <t>305717</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>275070</t>
+          <t>275510</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>314006</t>
+          <t>315061</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>554655</t>
+          <t>559333</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>608988</t>
+          <t>610213</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,58%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21381</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24750</t>
+          <t>24745</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40319</t>
+          <t>40045</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28682</t>
+          <t>29729</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26151</t>
+          <t>25238</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20328</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46636</t>
+          <t>45463</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>167670</t>
+          <t>167948</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>190584</t>
+          <t>191298</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>175566</t>
+          <t>173818</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>197811</t>
+          <t>197778</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>352808</t>
+          <t>352230</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>384399</t>
+          <t>384388</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14655</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4662</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>19723</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18180</t>
+          <t>18824</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43609</t>
+          <t>44795</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>14011</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38554</t>
+          <t>37944</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38909</t>
+          <t>39569</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>74257</t>
+          <t>77036</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>216173</t>
+          <t>215377</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>242169</t>
+          <t>241688</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>226723</t>
+          <t>227153</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>252423</t>
+          <t>252263</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>451072</t>
+          <t>448146</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>487962</t>
+          <t>486108</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14940</t>
+          <t>14520</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38975</t>
+          <t>38480</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39436</t>
+          <t>39796</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>68495</t>
+          <t>68284</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>59895</t>
+          <t>61180</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>97535</t>
+          <t>97172</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>51245</t>
+          <t>52012</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>93633</t>
+          <t>91153</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>41401</t>
+          <t>44650</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>79589</t>
+          <t>80762</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>101726</t>
+          <t>102436</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>156297</t>
+          <t>157947</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>537592</t>
+          <t>539919</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>581605</t>
+          <t>582284</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>553846</t>
+          <t>553872</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>599342</t>
+          <t>597454</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1108092</t>
+          <t>1110051</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1171027</t>
+          <t>1170942</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>32912</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>64486</t>
+          <t>61682</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>26862</t>
+          <t>26656</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>52135</t>
+          <t>52140</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>66440</t>
+          <t>65420</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>104630</t>
+          <t>104788</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>45936</t>
+          <t>45973</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>83894</t>
+          <t>84292</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>49345</t>
+          <t>49078</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>92544</t>
+          <t>90411</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>104427</t>
+          <t>106277</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>160539</t>
+          <t>160314</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>645014</t>
+          <t>646861</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>691818</t>
+          <t>691156</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>696634</t>
+          <t>695666</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>743112</t>
+          <t>741003</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1356627</t>
+          <t>1354590</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1421395</t>
+          <t>1418854</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,42%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>178099</t>
+          <t>178617</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>239796</t>
+          <t>241047</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>203574</t>
+          <t>202153</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>262822</t>
+          <t>259728</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>397100</t>
+          <t>400298</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>486008</t>
+          <t>482043</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>275046</t>
+          <t>274204</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>357798</t>
+          <t>357739</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,7 +13189,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>284066</t>
+          <t>282727</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>371657</t>
+          <t>372028</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>588141</t>
+          <t>581689</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>707018</t>
+          <t>702024</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2821058</t>
+          <t>2821365</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2917402</t>
+          <t>2919471</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2934849</t>
+          <t>2934563</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3036508</t>
+          <t>3040168</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5784760</t>
+          <t>5789390</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5924398</t>
+          <t>5930353</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2023</t>
+          <t>Población según su lugar de nacimiento en 2023 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9224</t>
+          <t>9558</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15009</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18340</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26874</t>
+          <t>27157</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20558</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47625</t>
+          <t>45980</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18542</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33939</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43170</t>
+          <t>42549</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75580</t>
+          <t>74739</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>254537</t>
+          <t>255265</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>281136</t>
+          <t>282603</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>243717</t>
+          <t>242767</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>259620</t>
+          <t>259840</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>503696</t>
+          <t>503571</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>537182</t>
+          <t>537077</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9074</t>
+          <t>9153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>7707</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>12754</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19252</t>
+          <t>20901</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>51911</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32685</t>
+          <t>32893</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>42662</t>
+          <t>42677</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>77270</t>
+          <t>76002</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>466312</t>
+          <t>463661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>496328</t>
+          <t>494837</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>474333</t>
+          <t>473810</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>490483</t>
+          <t>490148</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>945372</t>
+          <t>946089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>979340</t>
+          <t>979816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>957</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>13020</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,82 +14793,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>13550</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8682</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>21180</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>6,11%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>20174</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>13529</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>29551</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>4,46%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13550</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8378</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20460</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>20174</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>13243</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>30208</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>300297</t>
+          <t>301134</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311648</t>
+          <t>311615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>323196</t>
+          <t>322742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>335811</t>
+          <t>335946</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>628391</t>
+          <t>628774</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>645396</t>
+          <t>644957</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>6902</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7672</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16096</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35036</t>
+          <t>36800</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36965</t>
+          <t>35221</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37636</t>
+          <t>37491</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62379</t>
+          <t>64994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>272338</t>
+          <t>270851</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>291812</t>
+          <t>291434</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>329129</t>
+          <t>331230</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>348131</t>
+          <t>348330</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>611340</t>
+          <t>608680</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>636789</t>
+          <t>636807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>171261</t>
+          <t>170849</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>176066</t>
+          <t>175847</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>194887</t>
+          <t>194613</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>201025</t>
+          <t>201293</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>368547</t>
+          <t>367990</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>376020</t>
+          <t>376435</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6323</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15616</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27157</t>
+          <t>26113</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>251695</t>
+          <t>251766</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>262266</t>
+          <t>262459</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>238482</t>
+          <t>238813</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>248514</t>
+          <t>248362</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>493839</t>
+          <t>494807</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>508610</t>
+          <t>509440</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>18006</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>25674</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27453</t>
+          <t>27520</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>36607</t>
+          <t>37450</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>47725</t>
+          <t>48450</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>81819</t>
+          <t>83294</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>45571</t>
+          <t>46242</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>70482</t>
+          <t>71005</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>100998</t>
+          <t>102386</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>144191</t>
+          <t>144037</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>523779</t>
+          <t>522656</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>557369</t>
+          <t>557341</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>550516</t>
+          <t>549680</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>576902</t>
+          <t>574965</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1081024</t>
+          <t>1081855</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1126028</t>
+          <t>1125722</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,47%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7123</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,7 +16995,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>13859</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>20190</t>
+          <t>20015</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>17388</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14607</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>32414</t>
+          <t>32992</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>658441</t>
+          <t>659141</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>672532</t>
+          <t>672756</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>685970</t>
+          <t>686550</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>698488</t>
+          <t>698920</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1349794</t>
+          <t>1350357</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1368474</t>
+          <t>1368757</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>36091</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>46288</t>
+          <t>45613</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>53900</t>
+          <t>53601</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>66827</t>
+          <t>66061</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>92172</t>
+          <t>92570</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>107747</t>
+          <t>108929</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>151201</t>
+          <t>151383</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>212061</t>
+          <t>211277</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>150494</t>
+          <t>150137</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>192042</t>
+          <t>192495</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>311933</t>
+          <t>315783</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>387820</t>
+          <t>391168</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2954531</t>
+          <t>2954503</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3015303</t>
+          <t>3013607</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3083494</t>
+          <t>3082487</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3127588</t>
+          <t>3128547</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6055076</t>
+          <t>6048659</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6132702</t>
+          <t>6126963</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
